--- a/casebase/statistics/record.xlsx
+++ b/casebase/statistics/record.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\0_code\block-gml-casebase\casebase\statistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1E737B7-05CC-4BEF-AC0F-4BE8FA43559A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06522F98-1B63-4FF6-AE7E-1101BC1040E1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="25824" windowHeight="15504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="25824" windowHeight="15504" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Block" sheetId="1" r:id="rId1"/>
     <sheet name="LoD1" sheetId="2" r:id="rId2"/>
     <sheet name="LoD2" sheetId="3" r:id="rId3"/>
+    <sheet name="汇总" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="180">
   <si>
     <t>city</t>
   </si>
@@ -384,9 +385,6 @@
     <t>.json</t>
   </si>
   <si>
-    <t>7145 (28992)</t>
-  </si>
-  <si>
     <t>数据质量不如lod2</t>
   </si>
   <si>
@@ -465,9 +463,6 @@
     <t>https://github.com/AICyberTeam/GABLE</t>
   </si>
   <si>
-    <t>顶点过多，需要simplify，效果不好，失去形状</t>
-  </si>
-  <si>
     <t>https://www.stadt-zuerich.ch/geodaten/download/Bauten___Blockmodell?format=10007</t>
   </si>
   <si>
@@ -519,9 +514,6 @@
     <t>https://data.namur.be/explore/dataset/namur-3d-batiments-textures-par-dalle-de-200m/table/?dataChart=eyJxdWVyaWVzIjpbeyJjb25maWciOnsiZGF0YXNldCI6Im5hbXVyLTNkLWJhdGltZW50cy10ZXh0dXJlcy1wYXItZGFsbGUtZGUtMjAwbSIsIm9wdGlvbnMiOnt9fSwiY2hhcnRzIjpbeyJhbGlnbk1vbnRoIjp0cnVlLCJ0eXBlIjoiY29sdW1uIiwiZnVuYyI6IkNPVU5UIiwic2NpZW50aWZpY0Rpc3BsYXkiOnRydWUsImNvbG9yIjoiIzAxMUY0OSJ9XSwieEF4aXMiOiJub20iLCJtYXhwb2ludHMiOjUwLCJzb3J0IjoiIn1dLCJ0aW1lc2NhbGUiOiIiLCJkaXNwbGF5TGVnZW5kIjp0cnVlLCJhbGlnbk1vbnRoIjp0cnVlfQ%3D%3D&amp;location=13,50.43269,4.86943&amp;basemap=jawg.streets</t>
   </si>
   <si>
-    <t>通过法向量判断surface语义有bug</t>
-  </si>
-  <si>
     <t>https://geoportalpraha.cz/en/data-and-services/7e6316e95cfe4f36ae06bbfb687bf34b</t>
   </si>
   <si>
@@ -538,9 +530,6 @@
   </si>
   <si>
     <t>https://geoportaal.maaamet.ee/eng/Download-3D-data-p837.html</t>
-  </si>
-  <si>
-    <t>通过法向量判断surface语义有小bug，数据质量较差</t>
   </si>
   <si>
     <t>https://geodaten.bayern.de/opengeodata/OpenDataDetail.html?pn=lod2</t>
@@ -557,6 +546,30 @@
   </si>
   <si>
     <t>截断数据后lod1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（数据不可用）通过法向量判断surface语义有bug</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（数据不可用）通过法向量判断surface语义有小bug，数据质量较差</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（数据不可用）顶点过多，需要simplify，效果不好，失去形状</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>总lod1 block（根据指标筛除不可用）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>总lod2 block（根据指标筛除不可用）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7415 (28992)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -704,7 +717,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -743,9 +756,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="3" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1067,7 +1077,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
@@ -1085,7 +1095,7 @@
     <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1122,23 +1132,8 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
@@ -1175,27 +1170,8 @@
       <c r="L2" s="1">
         <v>4903</v>
       </c>
-      <c r="M2" s="1">
-        <f>SUM(H2:H46)</f>
-        <v>261978</v>
-      </c>
-      <c r="N2" s="1">
-        <f>SUM(I2:I46)</f>
-        <v>79550</v>
-      </c>
-      <c r="O2" s="1">
-        <f>SUM(K2:K50)</f>
-        <v>208344</v>
-      </c>
-      <c r="P2" s="1">
-        <f>SUM(L2:L46)</f>
-        <v>46276</v>
-      </c>
-      <c r="Q2" s="1">
-        <v>181858</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
@@ -1233,7 +1209,7 @@
         <v>5571</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>22</v>
       </c>
@@ -1271,7 +1247,7 @@
         <v>2957</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>25</v>
       </c>
@@ -1303,7 +1279,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>29</v>
       </c>
@@ -1341,7 +1317,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>32</v>
       </c>
@@ -1379,7 +1355,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>34</v>
       </c>
@@ -1411,7 +1387,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>36</v>
       </c>
@@ -1443,219 +1419,223 @@
         <v>879</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="6" t="s">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="9">
+      <c r="C10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="1">
         <v>20260424</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="1">
         <v>20260424</v>
       </c>
-      <c r="F10" s="9">
-        <v>176.09</v>
-      </c>
-      <c r="G10" s="9">
-        <v>998</v>
-      </c>
-      <c r="I10" s="9">
-        <v>752</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F10" s="1">
+        <v>495.89</v>
+      </c>
+      <c r="G10" s="1">
+        <v>6644</v>
+      </c>
+      <c r="I10" s="1">
+        <v>4949</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10" s="1">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>42</v>
+      <c r="C11" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="D11" s="1">
-        <v>20260424</v>
+        <v>20260425</v>
       </c>
       <c r="E11" s="1">
-        <v>20260424</v>
+        <v>20260425</v>
       </c>
       <c r="F11" s="1">
-        <v>495.89</v>
+        <v>328.28</v>
       </c>
       <c r="G11" s="1">
-        <v>6644</v>
+        <v>2766</v>
+      </c>
+      <c r="H11" s="1">
+        <v>2268</v>
       </c>
       <c r="I11" s="1">
-        <v>4949</v>
+        <v>2268</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
+      </c>
+      <c r="K11" s="1">
+        <v>2154</v>
       </c>
       <c r="L11" s="1">
-        <v>4700</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="3" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="10">
+        <v>20260425</v>
+      </c>
+      <c r="E12" s="10">
+        <v>20260425</v>
+      </c>
+      <c r="F12" s="10">
+        <v>1218.72</v>
+      </c>
+      <c r="G12" s="10">
+        <v>35288</v>
+      </c>
+      <c r="H12" s="10">
+        <v>2743</v>
+      </c>
+      <c r="I12" s="10">
+        <v>28926</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K12" s="1">
+        <v>2598</v>
+      </c>
+      <c r="L12" s="10"/>
+    </row>
+    <row r="13" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="1">
+      <c r="C13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="1">
         <v>20260425</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E13" s="1">
         <v>20260425</v>
       </c>
-      <c r="F12" s="1">
-        <v>328.28</v>
-      </c>
-      <c r="G12" s="1">
-        <v>2766</v>
-      </c>
-      <c r="H12" s="1">
-        <v>2268</v>
-      </c>
-      <c r="I12" s="1">
-        <v>2268</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K12" s="1">
-        <v>2154</v>
-      </c>
-      <c r="L12" s="1">
-        <v>2154</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="10">
-        <v>20260425</v>
-      </c>
-      <c r="E13" s="10">
-        <v>20260425</v>
-      </c>
-      <c r="F13" s="10">
-        <v>1218.72</v>
-      </c>
-      <c r="G13" s="10">
-        <v>35288</v>
-      </c>
-      <c r="H13" s="10">
-        <v>2743</v>
-      </c>
-      <c r="I13" s="10">
-        <v>28926</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>48</v>
+      <c r="F13" s="1">
+        <v>128.77000000000001</v>
+      </c>
+      <c r="G13" s="1">
+        <v>4041</v>
+      </c>
+      <c r="H13" s="1">
+        <v>2793</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2793</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="K13" s="1">
-        <v>2598</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>49</v>
+        <v>2650</v>
+      </c>
+      <c r="L13" s="1">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D14" s="1">
-        <v>20260425</v>
+        <v>20260413</v>
       </c>
       <c r="E14" s="1">
-        <v>20260425</v>
+        <v>20260413</v>
       </c>
       <c r="F14" s="1">
-        <v>128.77000000000001</v>
+        <v>860.69</v>
       </c>
       <c r="G14" s="1">
-        <v>4041</v>
+        <v>11999</v>
       </c>
       <c r="H14" s="1">
-        <v>2793</v>
+        <v>9191</v>
       </c>
       <c r="I14" s="1">
-        <v>2793</v>
+        <v>9229</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K14" s="1">
-        <v>2650</v>
+        <v>8726</v>
       </c>
       <c r="L14" s="1">
-        <v>2650</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>16</v>
+        <v>8762</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="D15" s="1">
-        <v>20260413</v>
+        <v>20260427</v>
       </c>
       <c r="E15" s="1">
-        <v>20260413</v>
+        <v>20260427</v>
       </c>
       <c r="F15" s="1">
-        <v>860.69</v>
+        <v>600.92999999999995</v>
       </c>
       <c r="G15" s="1">
-        <v>11999</v>
+        <v>5825</v>
       </c>
       <c r="H15" s="1">
-        <v>9191</v>
-      </c>
-      <c r="I15" s="1">
-        <v>9229</v>
+        <v>4732</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K15" s="1">
-        <v>8726</v>
-      </c>
-      <c r="L15" s="1">
-        <v>8762</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+        <v>4495</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>26</v>
@@ -1670,24 +1650,24 @@
         <v>20260427</v>
       </c>
       <c r="F16" s="1">
-        <v>600.92999999999995</v>
+        <v>606.78</v>
       </c>
       <c r="G16" s="1">
-        <v>5825</v>
+        <v>19484</v>
       </c>
       <c r="H16" s="1">
-        <v>4732</v>
+        <v>16898</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K16" s="1">
-        <v>4495</v>
+        <v>16044</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>26</v>
@@ -1702,24 +1682,24 @@
         <v>20260427</v>
       </c>
       <c r="F17" s="1">
-        <v>606.78</v>
+        <v>246.03</v>
       </c>
       <c r="G17" s="1">
-        <v>19484</v>
+        <v>5024</v>
       </c>
       <c r="H17" s="1">
-        <v>16898</v>
+        <v>4015</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K17" s="1">
-        <v>16044</v>
+        <v>3803</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>26</v>
@@ -1728,30 +1708,30 @@
         <v>47</v>
       </c>
       <c r="D18" s="1">
-        <v>20260427</v>
+        <v>20260428</v>
       </c>
       <c r="E18" s="1">
-        <v>20260427</v>
+        <v>20260428</v>
       </c>
       <c r="F18" s="1">
-        <v>246.03</v>
+        <v>177.21</v>
       </c>
       <c r="G18" s="1">
-        <v>5024</v>
+        <v>5800</v>
       </c>
       <c r="H18" s="1">
-        <v>4015</v>
+        <v>4564</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K18" s="1">
-        <v>3803</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>59</v>
+      <c r="A19" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>26</v>
@@ -1766,30 +1746,30 @@
         <v>20260428</v>
       </c>
       <c r="F19" s="1">
-        <v>177.21</v>
+        <v>374.28</v>
       </c>
       <c r="G19" s="1">
-        <v>5800</v>
+        <v>10442</v>
       </c>
       <c r="H19" s="1">
-        <v>4564</v>
+        <v>9377</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K19" s="1">
-        <v>4330</v>
+        <v>8902</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="D20" s="1">
         <v>20260428</v>
@@ -1797,25 +1777,25 @@
       <c r="E20" s="1">
         <v>20260428</v>
       </c>
-      <c r="F20" s="1">
-        <v>374.28</v>
+      <c r="F20" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="G20" s="1">
-        <v>10442</v>
+        <v>101419</v>
       </c>
       <c r="H20" s="1">
-        <v>9377</v>
+        <v>58668</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K20" s="1">
-        <v>8902</v>
+        <v>55731</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>63</v>
+      <c r="A21" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>64</v>
@@ -1829,25 +1809,25 @@
       <c r="E21" s="1">
         <v>20260428</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>66</v>
+      <c r="F21" s="1">
+        <v>1120.43</v>
       </c>
       <c r="G21" s="1">
-        <v>101419</v>
+        <v>31897</v>
       </c>
       <c r="H21" s="1">
-        <v>58668</v>
+        <v>29955</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K21" s="1">
-        <v>55731</v>
+        <v>28457</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>68</v>
+      <c r="A22" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>64</v>
@@ -1856,30 +1836,30 @@
         <v>65</v>
       </c>
       <c r="D22" s="1">
-        <v>20260428</v>
+        <v>20260416</v>
       </c>
       <c r="E22" s="1">
-        <v>20260428</v>
+        <v>20260416</v>
       </c>
       <c r="F22" s="1">
-        <v>1120.43</v>
+        <v>289.58999999999997</v>
       </c>
       <c r="G22" s="1">
-        <v>31897</v>
+        <v>26208</v>
       </c>
       <c r="H22" s="1">
-        <v>29955</v>
+        <v>23443</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K22" s="1">
-        <v>28457</v>
+        <v>22265</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>70</v>
+      <c r="A23" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>64</v>
@@ -1888,36 +1868,36 @@
         <v>65</v>
       </c>
       <c r="D23" s="1">
-        <v>20260416</v>
+        <v>20260429</v>
       </c>
       <c r="E23" s="1">
-        <v>20260416</v>
+        <v>20260429</v>
       </c>
       <c r="F23" s="1">
-        <v>289.58999999999997</v>
+        <v>732.23</v>
       </c>
       <c r="G23" s="1">
-        <v>26208</v>
+        <v>11389</v>
       </c>
       <c r="H23" s="1">
-        <v>23443</v>
+        <v>10052</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K23" s="1">
-        <v>22265</v>
+        <v>9549</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>72</v>
+      <c r="A24" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="D24" s="1">
         <v>20260429</v>
@@ -1926,93 +1906,94 @@
         <v>20260429</v>
       </c>
       <c r="F24" s="1">
-        <v>732.23</v>
+        <v>665.58</v>
       </c>
       <c r="G24" s="1">
-        <v>11389</v>
+        <v>12346</v>
       </c>
       <c r="H24" s="1">
-        <v>10052</v>
+        <v>10107</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K24" s="1">
-        <v>9549</v>
+        <v>9594</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" s="5">
-        <v>20260424</v>
-      </c>
-      <c r="E25" s="5">
-        <v>20260424</v>
-      </c>
-      <c r="F25" s="5">
-        <v>159.41999999999999</v>
-      </c>
-      <c r="G25" s="5">
-        <v>1624</v>
-      </c>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5">
-        <v>1119</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="K25" s="5"/>
+      <c r="A25" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="1">
+        <v>20260430</v>
+      </c>
+      <c r="E25" s="1">
+        <v>20260430</v>
+      </c>
+      <c r="F25" s="1">
+        <v>475.21</v>
+      </c>
+      <c r="G25" s="1">
+        <v>7480</v>
+      </c>
+      <c r="H25" s="1">
+        <v>5414</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K25" s="1">
+        <v>5142</v>
+      </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>27</v>
+        <v>81</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="D26" s="1">
-        <v>20260429</v>
+        <v>20260430</v>
       </c>
       <c r="E26" s="1">
-        <v>20260429</v>
+        <v>20260430</v>
       </c>
       <c r="F26" s="1">
-        <v>665.58</v>
+        <v>310.74</v>
       </c>
       <c r="G26" s="1">
-        <v>12346</v>
-      </c>
-      <c r="H26" s="1">
-        <v>10107</v>
+        <v>6224</v>
+      </c>
+      <c r="I26" s="1">
+        <v>5085</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="K26" s="1">
-        <v>9594</v>
+        <v>82</v>
+      </c>
+      <c r="L26" s="1">
+        <v>4823</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>27</v>
+      <c r="A27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="D27" s="1">
         <v>20260430</v>
@@ -2021,283 +2002,279 @@
         <v>20260430</v>
       </c>
       <c r="F27" s="1">
-        <v>475.21</v>
+        <v>186.62</v>
       </c>
       <c r="G27" s="1">
-        <v>7480</v>
-      </c>
-      <c r="H27" s="1">
-        <v>5414</v>
+        <v>2281</v>
+      </c>
+      <c r="I27" s="1">
+        <v>1844</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="K27" s="1">
-        <v>5142</v>
+        <v>84</v>
+      </c>
+      <c r="L27" s="1">
+        <v>1748</v>
       </c>
     </row>
     <row r="28" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D28" s="1">
-        <v>20260430</v>
+        <v>20260414</v>
       </c>
       <c r="E28" s="1">
-        <v>20260430</v>
+        <v>20260414</v>
       </c>
       <c r="F28" s="1">
-        <v>310.74</v>
+        <v>51.59</v>
       </c>
       <c r="G28" s="1">
-        <v>6224</v>
+        <v>674</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1">
-        <v>5085</v>
+        <v>516</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1">
-        <v>4823</v>
+        <v>490</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>83</v>
+      <c r="A29" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>16</v>
+      <c r="C29" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="D29" s="1">
-        <v>20260430</v>
+        <v>20260507</v>
       </c>
       <c r="E29" s="1">
-        <v>20260430</v>
+        <v>20260507</v>
       </c>
       <c r="F29" s="1">
-        <v>186.62</v>
+        <v>140.63999999999999</v>
       </c>
       <c r="G29" s="1">
-        <v>2281</v>
-      </c>
-      <c r="I29" s="1">
-        <v>1844</v>
+        <v>1789</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1204</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="L29" s="1">
-        <v>1748</v>
+        <v>92</v>
+      </c>
+      <c r="K29" s="1">
+        <v>1142</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D30" s="9">
-        <v>20260504</v>
-      </c>
-      <c r="E30" s="9">
-        <v>20260504</v>
-      </c>
-      <c r="F30" s="9">
-        <v>16504.82</v>
-      </c>
-      <c r="G30" s="9">
-        <v>69270</v>
-      </c>
-      <c r="H30" s="9">
-        <v>42014</v>
-      </c>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K30" s="9"/>
+      <c r="A30" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" s="1">
+        <v>20260507</v>
+      </c>
+      <c r="E30" s="1">
+        <v>20260507</v>
+      </c>
+      <c r="F30" s="1">
+        <v>47.98</v>
+      </c>
+      <c r="G30" s="1">
+        <v>1877</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1591</v>
+      </c>
+      <c r="I30" s="1">
+        <v>1589</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K30" s="1">
+        <v>1511</v>
+      </c>
+      <c r="L30" s="1">
+        <v>1508</v>
+      </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B31" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>30</v>
+      <c r="C31" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="D31" s="1">
-        <v>20260414</v>
+        <v>20260507</v>
       </c>
       <c r="E31" s="1">
-        <v>20260414</v>
+        <v>20260507</v>
       </c>
       <c r="F31" s="1">
-        <v>51.59</v>
+        <v>105.31</v>
       </c>
       <c r="G31" s="1">
-        <v>674</v>
-      </c>
-      <c r="I31" s="1">
-        <v>516</v>
+        <v>4662</v>
+      </c>
+      <c r="H31" s="1">
+        <v>3614</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="L31" s="1">
-        <v>490</v>
+        <v>97</v>
+      </c>
+      <c r="K31" s="1">
+        <v>3431</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B32" s="3" t="s">
+      <c r="A32" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D32" s="1">
-        <v>20260507</v>
+        <v>20260508</v>
       </c>
       <c r="E32" s="1">
-        <v>20260507</v>
+        <v>20260508</v>
       </c>
       <c r="F32" s="1">
-        <v>140.63999999999999</v>
+        <v>242.16</v>
       </c>
       <c r="G32" s="1">
-        <v>1789</v>
+        <v>3352</v>
       </c>
       <c r="H32" s="1">
-        <v>1204</v>
+        <v>2536</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="K32" s="1">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B33" s="1" t="s">
+        <v>2409</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D33" s="1">
-        <v>20260507</v>
-      </c>
-      <c r="E33" s="1">
-        <v>20260507</v>
-      </c>
-      <c r="F33" s="1">
-        <v>47.98</v>
-      </c>
-      <c r="G33" s="1">
-        <v>1877</v>
-      </c>
-      <c r="H33" s="1">
-        <v>1591</v>
-      </c>
-      <c r="I33" s="1">
-        <v>1589</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="K33" s="1">
-        <v>1511</v>
-      </c>
-      <c r="L33" s="1">
-        <v>1508</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B34" s="1" t="s">
+      <c r="C51" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D51" s="9">
+        <v>20260424</v>
+      </c>
+      <c r="E51" s="9">
+        <v>20260424</v>
+      </c>
+      <c r="F51" s="9">
+        <v>176.09</v>
+      </c>
+      <c r="G51" s="9">
+        <v>998</v>
+      </c>
+      <c r="I51" s="9">
+        <v>752</v>
+      </c>
+      <c r="J51" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D52" s="9">
+        <v>20260504</v>
+      </c>
+      <c r="E52" s="9">
+        <v>20260504</v>
+      </c>
+      <c r="F52" s="9">
+        <v>16504.82</v>
+      </c>
+      <c r="G52" s="9">
+        <v>69270</v>
+      </c>
+      <c r="H52" s="9">
+        <v>42014</v>
+      </c>
+      <c r="I52" s="9"/>
+      <c r="J52" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="K52" s="9"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B53" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D34" s="1">
-        <v>20260507</v>
-      </c>
-      <c r="E34" s="1">
-        <v>20260507</v>
-      </c>
-      <c r="F34" s="1">
-        <v>105.31</v>
-      </c>
-      <c r="G34" s="1">
-        <v>4662</v>
-      </c>
-      <c r="H34" s="1">
-        <v>3614</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="K34" s="1">
-        <v>3431</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D35" s="1">
-        <v>20260508</v>
-      </c>
-      <c r="E35" s="1">
-        <v>20260508</v>
-      </c>
-      <c r="F35" s="1">
-        <v>242.16</v>
-      </c>
-      <c r="G35" s="1">
-        <v>3352</v>
-      </c>
-      <c r="H35" s="1">
-        <v>2536</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="K35" s="1">
-        <v>2409</v>
-      </c>
+      <c r="C53" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D53" s="5">
+        <v>20260424</v>
+      </c>
+      <c r="E53" s="5">
+        <v>20260424</v>
+      </c>
+      <c r="F53" s="5">
+        <v>159.41999999999999</v>
+      </c>
+      <c r="G53" s="5">
+        <v>1624</v>
+      </c>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5">
+        <v>1119</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="K53" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2368,22 +2345,7 @@
       <c r="L1" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="M1"/>
-      <c r="O1" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="P1" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q1" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="R1" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="S1" s="12" t="s">
-        <v>115</v>
-      </c>
+      <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:25" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -2418,26 +2380,6 @@
       </c>
       <c r="K2" s="3">
         <v>3.46</v>
-      </c>
-      <c r="O2" s="12">
-        <f>COUNTA(A2:A30)</f>
-        <v>25</v>
-      </c>
-      <c r="P2" s="12">
-        <f>SUM(G2:G31)</f>
-        <v>13621447</v>
-      </c>
-      <c r="Q2" s="12">
-        <f>SUM(H2:H31)</f>
-        <v>146597931</v>
-      </c>
-      <c r="R2" s="12">
-        <f>SUM(J2:J31)</f>
-        <v>12187282</v>
-      </c>
-      <c r="S2" s="12">
-        <f>SUM(K2:K30)</f>
-        <v>67.350000000000009</v>
       </c>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
@@ -2453,7 +2395,7 @@
         <v>118</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D3" s="3">
         <v>20250903</v>
@@ -2471,7 +2413,7 @@
         <v>1541016</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="J3" s="3">
         <v>146861</v>
@@ -2480,9 +2422,9 @@
         <v>1.01</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="M3"/>
+        <v>120</v>
+      </c>
+      <c r="M3" s="1"/>
       <c r="X3" s="7"/>
     </row>
     <row r="4" spans="1:25" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2490,7 +2432,7 @@
         <v>44</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C4" s="3">
         <v>1</v>
@@ -2502,7 +2444,7 @@
         <v>20260424</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G4" s="3">
         <v>163530</v>
@@ -2519,14 +2461,14 @@
       <c r="K4" s="3">
         <v>0.9</v>
       </c>
-      <c r="M4"/>
+      <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:25" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>51</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="3">
         <v>1</v>
@@ -2538,7 +2480,7 @@
         <v>20260427</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G5" s="3">
         <v>928002</v>
@@ -2555,7 +2497,7 @@
       <c r="K5" s="3">
         <v>6.6</v>
       </c>
-      <c r="M5"/>
+      <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
@@ -2565,7 +2507,7 @@
         <v>118</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D6" s="3">
         <v>20250903</v>
@@ -2574,7 +2516,7 @@
         <v>20260425</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G6" s="3">
         <v>189648</v>
@@ -2583,7 +2525,7 @@
         <v>1568129</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="J6" s="3">
         <v>154001</v>
@@ -2592,16 +2534,16 @@
         <v>1.04</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="M6"/>
+        <v>120</v>
+      </c>
+      <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:25" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C7" s="3">
         <v>1</v>
@@ -2613,7 +2555,7 @@
         <v>20260427</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G7" s="3">
         <v>10300</v>
@@ -2631,7 +2573,7 @@
         <v>0.05</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -2639,7 +2581,7 @@
         <v>53</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C8" s="3">
         <v>1</v>
@@ -2651,7 +2593,7 @@
         <v>20260427</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G8" s="3">
         <v>159456</v>
@@ -2669,16 +2611,16 @@
         <v>0.15</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="M8"/>
+        <v>128</v>
+      </c>
+      <c r="M8" s="1"/>
     </row>
     <row r="9" spans="1:25" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C9" s="3">
         <v>1</v>
@@ -2690,7 +2632,7 @@
         <v>20260427</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G9" s="3">
         <v>1617647</v>
@@ -2707,14 +2649,14 @@
       <c r="K9" s="3">
         <v>1.43</v>
       </c>
-      <c r="M9"/>
+      <c r="M9" s="1"/>
     </row>
     <row r="10" spans="1:25" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>57</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
@@ -2726,7 +2668,7 @@
         <v>20260427</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G10" s="3">
         <v>123192</v>
@@ -2743,14 +2685,14 @@
       <c r="K10" s="3">
         <v>0.11</v>
       </c>
-      <c r="M10"/>
+      <c r="M10" s="1"/>
     </row>
     <row r="11" spans="1:25" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>59</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
@@ -2762,7 +2704,7 @@
         <v>20260428</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G11" s="3">
         <v>161911</v>
@@ -2779,7 +2721,7 @@
       <c r="K11" s="3">
         <v>0.19</v>
       </c>
-      <c r="M11"/>
+      <c r="M11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -2792,7 +2734,7 @@
         <v>46</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C12" s="3">
         <v>1</v>
@@ -2804,7 +2746,7 @@
         <v>20260428</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G12" s="3">
         <v>42974</v>
@@ -2822,16 +2764,16 @@
         <v>0.05</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="M12"/>
+        <v>133</v>
+      </c>
+      <c r="M12" s="1"/>
     </row>
     <row r="13" spans="1:25" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>61</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C13" s="3">
         <v>1</v>
@@ -2843,7 +2785,7 @@
         <v>20260428</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G13" s="3">
         <v>296701</v>
@@ -2860,14 +2802,14 @@
       <c r="K13" s="3">
         <v>0.3</v>
       </c>
-      <c r="M13"/>
+      <c r="M13" s="1"/>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>63</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -2879,7 +2821,7 @@
         <v>20260428</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G14" s="3">
         <v>2005288</v>
@@ -2897,16 +2839,16 @@
         <v>31.3</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="M14"/>
+        <v>136</v>
+      </c>
+      <c r="M14" s="1"/>
     </row>
     <row r="15" spans="1:25" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="C15" s="3">
         <v>1</v>
@@ -2918,7 +2860,7 @@
         <v>20260428</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G15" s="3">
         <v>646474</v>
@@ -2935,14 +2877,14 @@
       <c r="K15" s="3">
         <v>7.52</v>
       </c>
-      <c r="M15"/>
+      <c r="M15" s="1"/>
     </row>
     <row r="16" spans="1:25" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>70</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C16" s="3">
         <v>1</v>
@@ -2954,7 +2896,7 @@
         <v>20260421</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G16" s="3">
         <v>616119</v>
@@ -2971,14 +2913,14 @@
       <c r="K16" s="3">
         <v>7.87</v>
       </c>
-      <c r="M16"/>
+      <c r="M16" s="1"/>
     </row>
     <row r="17" spans="1:13" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>72</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C17" s="3">
         <v>1</v>
@@ -2990,7 +2932,7 @@
         <v>20260429</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G17" s="3">
         <v>213878</v>
@@ -3007,14 +2949,14 @@
       <c r="K17" s="3">
         <v>2.37</v>
       </c>
-      <c r="M17"/>
+      <c r="M17" s="1"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>77</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C18" s="3">
         <v>1</v>
@@ -3026,7 +2968,7 @@
         <v>20260429</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G18" s="3">
         <v>409703</v>
@@ -3043,14 +2985,14 @@
       <c r="K18" s="3">
         <v>0.28999999999999998</v>
       </c>
-      <c r="M18"/>
+      <c r="M18" s="1"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C19" s="3">
         <v>1.4</v>
@@ -3062,7 +3004,7 @@
         <v>20260429</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G19" s="3">
         <v>695635</v>
@@ -3079,14 +3021,14 @@
       <c r="K19" s="3">
         <v>0.26</v>
       </c>
-      <c r="M19"/>
+      <c r="M19" s="1"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>79</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C20" s="3">
         <v>1</v>
@@ -3098,7 +3040,7 @@
         <v>20260430</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G20" s="3">
         <v>282398</v>
@@ -3115,14 +3057,14 @@
       <c r="K20" s="3">
         <v>0.28999999999999998</v>
       </c>
-      <c r="M20"/>
-    </row>
-    <row r="21" spans="1:13" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M20" s="1"/>
+    </row>
+    <row r="21" spans="1:13" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>85</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C21" s="6">
         <v>1</v>
@@ -3134,7 +3076,7 @@
         <v>20260415</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G21" s="6">
         <v>4088130</v>
@@ -3142,7 +3084,7 @@
       <c r="H21" s="6">
         <v>59562180</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="9">
         <v>4490</v>
       </c>
       <c r="J21" s="6">
@@ -3152,7 +3094,7 @@
         <v>1.79</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -3160,7 +3102,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C22" s="3">
         <v>1</v>
@@ -3172,7 +3114,7 @@
         <v>20260506</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G22" s="3">
         <v>65986</v>
@@ -3189,14 +3131,14 @@
       <c r="K22" s="3">
         <v>0.15</v>
       </c>
-      <c r="M22"/>
+      <c r="M22" s="1"/>
     </row>
     <row r="23" spans="1:13" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>90</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C23" s="3">
         <v>1</v>
@@ -3208,7 +3150,7 @@
         <v>20260507</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G23" s="3">
         <v>54707</v>
@@ -3225,14 +3167,14 @@
       <c r="K23" s="3">
         <v>0.05</v>
       </c>
-      <c r="M23"/>
+      <c r="M23" s="1"/>
     </row>
     <row r="24" spans="1:13" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>96</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
@@ -3244,7 +3186,7 @@
         <v>20260508</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G24" s="3">
         <v>86053</v>
@@ -3262,16 +3204,16 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="M24"/>
+        <v>151</v>
+      </c>
+      <c r="M24" s="1"/>
     </row>
     <row r="25" spans="1:13" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>93</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C25" s="3">
         <v>1</v>
@@ -3283,7 +3225,7 @@
         <v>20260508</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G25" s="3">
         <v>59983</v>
@@ -3301,50 +3243,50 @@
         <v>0.03</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="M25"/>
+        <v>152</v>
+      </c>
+      <c r="M25" s="1"/>
     </row>
     <row r="26" spans="1:13" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="B26" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="C26" s="14">
+      <c r="B26" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C26" s="13">
         <v>1</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="13">
         <v>20260203</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E26" s="13">
         <v>20260508</v>
       </c>
-      <c r="F26" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="G26" s="14">
+      <c r="F26" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="G26" s="13">
         <v>153114</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H26" s="13">
         <v>1711200</v>
       </c>
       <c r="I26" s="3">
         <v>2154</v>
       </c>
-      <c r="J26" s="14">
+      <c r="J26" s="13">
         <v>108650</v>
       </c>
-      <c r="K26" s="14">
+      <c r="K26" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L26" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="M26"/>
-    </row>
-    <row r="27" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25"/>
+      <c r="L26" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="M26" s="1"/>
+    </row>
+    <row r="27" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
@@ -3359,7 +3301,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.77734375" style="3" customWidth="1"/>
@@ -3382,7 +3324,7 @@
     <col min="23" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>100</v>
       </c>
@@ -3405,7 +3347,7 @@
         <v>105</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>107</v>
@@ -3419,28 +3361,13 @@
       <c r="L1" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="P1" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q1" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="R1" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="S1" s="12" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C2" s="3">
         <v>2</v>
@@ -3452,7 +3379,7 @@
         <v>20260414</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G2" s="3">
         <v>388267</v>
@@ -3469,33 +3396,13 @@
       <c r="K2" s="3">
         <v>6.16</v>
       </c>
-      <c r="O2" s="12">
-        <f>COUNTA(A2:A30)</f>
-        <v>19</v>
-      </c>
-      <c r="P2" s="12">
-        <f>SUM(G2:G31)</f>
-        <v>4802552</v>
-      </c>
-      <c r="Q2" s="12">
-        <f>SUM(H2:H31)</f>
-        <v>72011604</v>
-      </c>
-      <c r="R2" s="12">
-        <f>SUM(J2:J31)</f>
-        <v>4331859</v>
-      </c>
-      <c r="S2" s="12">
-        <f>SUM(K2:K30)</f>
-        <v>86.720000000000013</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C3" s="3">
         <v>2.1</v>
@@ -3507,7 +3414,7 @@
         <v>20260416</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G3" s="3">
         <v>477126</v>
@@ -3525,7 +3432,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>22</v>
       </c>
@@ -3542,7 +3449,7 @@
         <v>20260414</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G4" s="3">
         <v>165992</v>
@@ -3551,7 +3458,7 @@
         <v>3236008</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="J4" s="3">
         <v>146861</v>
@@ -3560,12 +3467,12 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C5" s="3">
         <v>2</v>
@@ -3577,7 +3484,7 @@
         <v>20260422</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G5" s="3">
         <v>37885</v>
@@ -3595,15 +3502,15 @@
         <v>3.7</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C6" s="3">
         <v>2</v>
@@ -3615,7 +3522,7 @@
         <v>20260414</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G6" s="3">
         <v>50600</v>
@@ -3633,12 +3540,12 @@
         <v>7.41</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C7" s="3">
         <v>2.2000000000000002</v>
@@ -3650,7 +3557,7 @@
         <v>20260423</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G7" s="3">
         <v>23275</v>
@@ -3668,12 +3575,12 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="69" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C8" s="3">
         <v>2</v>
@@ -3685,7 +3592,7 @@
         <v>20260423</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G8" s="3">
         <v>135775</v>
@@ -3703,12 +3610,12 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C9" s="3">
         <v>2</v>
@@ -3720,7 +3627,7 @@
         <v>20260424</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G9" s="3">
         <v>68529</v>
@@ -3738,12 +3645,12 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>38</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C10" s="6">
         <v>2.2000000000000002</v>
@@ -3755,7 +3662,7 @@
         <v>20260424</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G10" s="6">
         <v>63153</v>
@@ -3773,15 +3680,15 @@
         <v>1.08</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C11" s="3">
         <v>2</v>
@@ -3793,7 +3700,7 @@
         <v>20260424</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G11" s="3">
         <v>366007</v>
@@ -3811,12 +3718,12 @@
         <v>4.72</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C12" s="3">
         <v>2</v>
@@ -3828,7 +3735,7 @@
         <v>20260424</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G12" s="3">
         <v>163576</v>
@@ -3846,12 +3753,12 @@
         <v>3.69</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>51</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C13" s="3">
         <v>2</v>
@@ -3863,7 +3770,7 @@
         <v>20260425</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G13" s="3">
         <v>874612</v>
@@ -3881,15 +3788,15 @@
         <v>14.3</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>46</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C14" s="11">
         <v>2</v>
@@ -3901,7 +3808,7 @@
         <v>20260425</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G14" s="11">
         <v>1083432</v>
@@ -3919,10 +3826,10 @@
         <v>12.8</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" s="11" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" s="11" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>49</v>
       </c>
@@ -3939,7 +3846,7 @@
         <v>20260425</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G15" s="3">
         <v>189649</v>
@@ -3948,7 +3855,7 @@
         <v>2910029</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="J15" s="3">
         <v>154002</v>
@@ -3957,12 +3864,12 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>74</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C16" s="6">
         <v>2</v>
@@ -3974,7 +3881,7 @@
         <v>20260429</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G16" s="6">
         <v>49790</v>
@@ -3992,7 +3899,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -4000,7 +3907,7 @@
         <v>81</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C17" s="3">
         <v>2</v>
@@ -4009,7 +3916,7 @@
         <v>20260430</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G17" s="3">
         <v>373913</v>
@@ -4032,7 +3939,7 @@
         <v>83</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C18" s="3">
         <v>2</v>
@@ -4041,7 +3948,7 @@
         <v>20260430</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G18" s="3">
         <v>219925</v>
@@ -4064,19 +3971,19 @@
         <v>88</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C19" s="3">
         <v>2</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E19" s="3">
         <v>20260506</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G19" s="3">
         <v>46569</v>
@@ -4099,7 +4006,7 @@
         <v>93</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C20" s="3">
         <v>2</v>
@@ -4111,7 +4018,7 @@
         <v>20260508</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G20" s="3">
         <v>24477</v>
@@ -4144,4 +4051,134 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId9"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B17D626-8753-457E-83E9-FDB6F70C6C5B}">
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="17.109375" customWidth="1"/>
+    <col min="18" max="18" width="14.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="H1" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="P1" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q1" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="R1" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="S1" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="T1" s="12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <f>SUM(Block!H2:H50)</f>
+        <v>219964</v>
+      </c>
+      <c r="B2" s="1">
+        <f>SUM(Block!I2:I50)</f>
+        <v>77679</v>
+      </c>
+      <c r="C2" s="1">
+        <f>SUM(Block!K2:K50)</f>
+        <v>208344</v>
+      </c>
+      <c r="D2" s="1">
+        <f>SUM(Block!L2:L50)</f>
+        <v>46276</v>
+      </c>
+      <c r="E2" s="1">
+        <v>181858</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="H2" s="12">
+        <f>COUNTA('LoD1'!A2:A30)</f>
+        <v>25</v>
+      </c>
+      <c r="I2" s="12">
+        <f>SUM('LoD1'!G2:G31)</f>
+        <v>13621447</v>
+      </c>
+      <c r="J2" s="12">
+        <f>SUM('LoD1'!H2:H31)</f>
+        <v>146597931</v>
+      </c>
+      <c r="K2" s="12">
+        <f>SUM('LoD1'!J2:J31)</f>
+        <v>12187282</v>
+      </c>
+      <c r="L2" s="12">
+        <f>SUM('LoD1'!K2:K30)</f>
+        <v>67.350000000000009</v>
+      </c>
+      <c r="P2" s="12">
+        <f>COUNTA('LoD2'!A2:A30)</f>
+        <v>19</v>
+      </c>
+      <c r="Q2" s="12">
+        <f>SUM('LoD2'!G2:G31)</f>
+        <v>4802552</v>
+      </c>
+      <c r="R2" s="12">
+        <f>SUM('LoD2'!H2:H31)</f>
+        <v>72011604</v>
+      </c>
+      <c r="S2" s="12">
+        <f>SUM('LoD2'!J2:J31)</f>
+        <v>4331859</v>
+      </c>
+      <c r="T2" s="12">
+        <f>SUM('LoD2'!K2:K30)</f>
+        <v>86.720000000000013</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
 </file>
--- a/casebase/statistics/record.xlsx
+++ b/casebase/statistics/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\0_code\block-gml-casebase\casebase\statistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06522F98-1B63-4FF6-AE7E-1101BC1040E1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07822701-F541-4AAE-8CED-8CCD9C668185}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="25824" windowHeight="15504" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="25824" windowHeight="15504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Block" sheetId="1" r:id="rId1"/>
@@ -1084,7 +1084,7 @@
     <col min="2" max="2" width="14.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="13.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="14.88671875" style="1" customWidth="1"/>
     <col min="8" max="9" width="9.109375" style="1" bestFit="1" customWidth="1"/>
@@ -1194,7 +1194,7 @@
         <v>7023</v>
       </c>
       <c r="H3" s="1">
-        <v>6547</v>
+        <v>6002</v>
       </c>
       <c r="I3" s="1">
         <v>5871</v>
@@ -4117,7 +4117,7 @@
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>SUM(Block!H2:H50)</f>
-        <v>219964</v>
+        <v>219419</v>
       </c>
       <c r="B2" s="1">
         <f>SUM(Block!I2:I50)</f>

--- a/casebase/statistics/record.xlsx
+++ b/casebase/statistics/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\0_code\block-gml-casebase\casebase\statistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07822701-F541-4AAE-8CED-8CCD9C668185}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E7CF01-640F-4F0D-9037-93E763163903}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="25824" windowHeight="15504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="25824" windowHeight="13320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Block" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="182">
   <si>
     <t>city</t>
   </si>
@@ -570,6 +570,14 @@
   </si>
   <si>
     <t>7415 (28992)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Datenlizenz Deutschland Namensnennung 2.0（dl-de/by-2-0）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2300,7 +2308,8 @@
     <col min="10" max="10" width="14.109375" style="3" customWidth="1"/>
     <col min="11" max="11" width="11.77734375" style="3" customWidth="1"/>
     <col min="12" max="12" width="23.88671875" style="3" customWidth="1"/>
-    <col min="13" max="15" width="9" style="3" customWidth="1"/>
+    <col min="13" max="13" width="35.88671875" style="3" customWidth="1"/>
+    <col min="14" max="15" width="9" style="3" customWidth="1"/>
     <col min="16" max="16" width="11.6640625" style="3" customWidth="1"/>
     <col min="17" max="17" width="12.5546875" style="3" customWidth="1"/>
     <col min="18" max="18" width="11.109375" style="3" customWidth="1"/>
@@ -2345,7 +2354,9 @@
       <c r="L1" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="M1" s="1"/>
+      <c r="M1" s="1" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="2" spans="1:25" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -2380,6 +2391,9 @@
       </c>
       <c r="K2" s="3">
         <v>3.46</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>181</v>
       </c>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
